--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824049</v>
+        <v>122824052</v>
       </c>
       <c r="B2" t="n">
-        <v>57369</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -774,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -784,12 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor hona</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824052</v>
+        <v>122824049</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>57369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,35 +814,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -902,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +907,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stor hona</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824052</v>
+        <v>122824049</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>57369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -761,7 +774,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +784,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stor hona</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824049</v>
+        <v>122824052</v>
       </c>
       <c r="B3" t="n">
-        <v>57369</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,48 +832,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -897,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,12 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stor hona</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>122824052</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824049</v>
+        <v>122824052</v>
       </c>
       <c r="B2" t="n">
-        <v>57369</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -774,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -784,12 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor hona</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824052</v>
+        <v>122824049</v>
       </c>
       <c r="B3" t="n">
-        <v>90972</v>
+        <v>57369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,35 +814,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -902,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +907,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stor hona</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824052</v>
+        <v>122824049</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>57369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -761,7 +774,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +784,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stor hona</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824049</v>
+        <v>122824052</v>
       </c>
       <c r="B3" t="n">
-        <v>57369</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,48 +832,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -897,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,12 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stor hona</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122824049</v>
       </c>
       <c r="B2" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>122824052</v>
       </c>
       <c r="B3" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>122824052</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>122824052</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824049</v>
+        <v>122824052</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -774,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -784,12 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor hona</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,15 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824052</v>
+        <v>122824049</v>
       </c>
       <c r="B3" t="n">
-        <v>90986</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,35 +804,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trinnehall, Sm</t>
@@ -902,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stor hona</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 41164-2023 artfynd.xlsx
+++ b/artfynd/A 41164-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122824052</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,8 +936,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122824049</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>